--- a/resource/groundTruths/requirement/CF_M01_ground_truth_requirement.xlsx
+++ b/resource/groundTruths/requirement/CF_M01_ground_truth_requirement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/requirement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60FF34BB-183F-844F-9633-F03D9084C5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE844D30-DEC6-C849-80DE-2B7C14F09E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14760" yWindow="900" windowWidth="14480" windowHeight="16580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="100">
   <si>
     <t>Document ID</t>
   </si>
@@ -38,16 +38,10 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>Categorization</t>
-  </si>
-  <si>
     <t>Related to</t>
   </si>
   <si>
     <t>Page Number</t>
-  </si>
-  <si>
-    <t>Applied Fixes</t>
   </si>
   <si>
     <t>CF_M01</t>
@@ -174,9 +168,6 @@
     <t>QR</t>
   </si>
   <si>
-    <t>Volere</t>
-  </si>
-  <si>
     <t>CF_M01_R19</t>
   </si>
   <si>
@@ -257,9 +248,6 @@
     <t>CF_M01_C02</t>
   </si>
   <si>
-    <t>Scalability</t>
-  </si>
-  <si>
     <t>CF_M01_C03</t>
   </si>
   <si>
@@ -335,7 +323,7 @@
     <t>*CF_M01_C10</t>
   </si>
   <si>
-    <t>*CF_M01_C11</t>
+    <t>Fixed Type</t>
   </si>
 </sst>
 </file>
@@ -675,10 +663,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -701,606 +689,585 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="H2">
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="H3">
+      <c r="G4">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4">
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5">
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6">
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7">
+      <c r="D14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9">
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
         <v>37</v>
       </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21">
         <v>38</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" t="s">
+        <v>80</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27">
         <v>39</v>
       </c>
-      <c r="D15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" t="s">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" t="s">
         <v>47</v>
       </c>
-      <c r="C19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="E29" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
         <v>87</v>
       </c>
-      <c r="F19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" t="s">
-        <v>53</v>
-      </c>
-      <c r="H20">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" t="s">
-        <v>54</v>
-      </c>
-      <c r="H22">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" t="s">
-        <v>50</v>
-      </c>
-      <c r="H23">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="C31" t="s">
         <v>84</v>
       </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" t="s">
-        <v>58</v>
-      </c>
-      <c r="H24">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" t="s">
-        <v>50</v>
-      </c>
-      <c r="H25">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" t="s">
-        <v>62</v>
-      </c>
-      <c r="H26">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" t="s">
-        <v>49</v>
-      </c>
-      <c r="E27" t="s">
-        <v>80</v>
-      </c>
-      <c r="F27" t="s">
-        <v>50</v>
-      </c>
-      <c r="H27">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" t="s">
-        <v>64</v>
-      </c>
-      <c r="H28">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" t="s">
-        <v>82</v>
-      </c>
-      <c r="F29" t="s">
-        <v>50</v>
-      </c>
-      <c r="H29">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="D31" t="s">
         <v>68</v>
       </c>
-      <c r="D30" t="s">
-        <v>15</v>
-      </c>
-      <c r="G30" t="s">
-        <v>69</v>
-      </c>
-      <c r="H30">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" t="s">
-        <v>71</v>
-      </c>
-      <c r="H31">
+      <c r="G31">
         <v>8</v>
       </c>
     </row>
@@ -1311,145 +1278,116 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>73</v>
       </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>74</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
         <v>92</v>
       </c>
-      <c r="D2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" t="s">
         <v>93</v>
-      </c>
-      <c r="D3">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D7">
-        <v>39</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B21" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/resource/groundTruths/requirement/CF_M01_ground_truth_requirement.xlsx
+++ b/resource/groundTruths/requirement/CF_M01_ground_truth_requirement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/requirement/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE844D30-DEC6-C849-80DE-2B7C14F09E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0F044A-9885-E745-A440-A3E38EB567C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14760" yWindow="900" windowWidth="14480" windowHeight="16580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="102">
   <si>
     <t>Document ID</t>
   </si>
@@ -324,6 +324,12 @@
   </si>
   <si>
     <t>Fixed Type</t>
+  </si>
+  <si>
+    <t>Maintainability</t>
+  </si>
+  <si>
+    <t>*CF_M01_C11</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1390,6 +1396,14 @@
         <v>79</v>
       </c>
     </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
